--- a/laporan_padel_dki_jakarta_2026-10-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-18.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.465.000</t>
+          <t>Rp3.663.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.930.000</t>
+          <t>Rp12.750.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>85</v>
       </c>
       <c r="D60" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.287.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp1.701.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp7.380.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp2.595.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp22.810.000</t>
+          <t>Rp22.560.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp69.000</t>
+          <t>Rp138.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.022.000</t>
+          <t>Rp5.103.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.675.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.870.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.865.000</t>
+          <t>Rp10.150.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.190.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-18.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.780.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.663.000</t>
+          <t>Rp3.762.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.750.000</t>
+          <t>Rp12.840.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.660.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.800.000</t>
+          <t>Rp12.100.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.045.000</t>
+          <t>Rp2.185.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.102.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.410.000</t>
+          <t>Rp3.535.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp546.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.695.000</t>
+          <t>Rp5.185.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.030.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp1.985.000</t>
+          <t>Rp2.245.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp11.395.000</t>
+          <t>Rp11.590.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.257.000</t>
+          <t>Rp4.356.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp435.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.701.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.374.500</t>
+          <t>Rp16.550.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.558.000</t>
+          <t>Rp12.448.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.670.000</t>
+          <t>Rp3.870.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.296.000</t>
+          <t>Rp4.796.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp11.600.000</t>
+          <t>Rp11.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.820.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp6.196.000</t>
+          <t>Rp6.796.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.325.000</t>
+          <t>Rp9.550.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp447.000</t>
+          <t>Rp618.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp11.242.000</t>
+          <t>Rp11.612.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp14.750.000</t>
+          <t>Rp16.150.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp22.560.000</t>
+          <t>Rp22.810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.425.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.738.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.000.000</t>
+          <t>Rp17.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.103.000</t>
+          <t>Rp5.265.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.145.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp21.850.000</t>
+          <t>Rp22.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.008.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp23.153.000</t>
+          <t>Rp25.246.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>128</v>
       </c>
       <c r="D42" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.093.000</t>
+          <t>Rp3.289.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.450.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>96</v>
       </c>
       <c r="D50" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.967.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D51" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.060.000</t>
+          <t>Rp17.310.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.990.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.150.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp808.500</t>
+          <t>Rp1.270.500</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.610.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.005.000</t>
+          <t>Rp5.730.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp12.250.000</t>
+          <t>Rp13.850.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp8.610.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.860.000</t>
+          <t>Rp7.420.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.704.000</t>
+          <t>Rp3.042.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-18.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.762.000</t>
+          <t>Rp4.158.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.232.000</t>
+          <t>Rp1.936.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.490.000</t>
+          <t>Rp12.820.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp3.486.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.270.000</t>
+          <t>Rp16.130.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp12.100.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.318.000</t>
+          <t>Rp2.838.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.185.000</t>
+          <t>Rp1.985.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.354.000</t>
+          <t>Rp3.483.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.456.000</t>
+          <t>Rp3.840.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.535.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.048.000</t>
+          <t>Rp2.757.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.554.000</t>
+          <t>Rp9.952.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.675.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.185.000</t>
+          <t>Rp5.820.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp395.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.140.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>85</v>
       </c>
       <c r="D60" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp555.000</t>
+          <t>Rp934.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.079.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.687.000</t>
+          <t>Rp2.886.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.245.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.356.000</t>
+          <t>Rp4.752.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.425.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.220.000</t>
+          <t>Rp3.470.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.187.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.595.000</t>
+          <t>Rp9.990.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.485.000</t>
+          <t>Rp4.885.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.796.000</t>
+          <t>Rp5.196.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp11.950.000</t>
+          <t>Rp13.300.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.350.000</t>
+          <t>Rp10.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp9.550.000</t>
+          <t>Rp9.975.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp5.174.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.260.000</t>
+          <t>Rp7.920.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp618.000</t>
+          <t>Rp951.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.690.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp11.612.000</t>
+          <t>Rp11.942.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp11.500.000</t>
+          <t>Rp12.300.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp16.150.000</t>
+          <t>Rp16.850.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp597.000</t>
+          <t>Rp995.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp2.856.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.595.000</t>
+          <t>Rp2.870.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp22.810.000</t>
+          <t>Rp23.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.015.000</t>
+          <t>Rp12.575.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.185.000</t>
+          <t>Rp16.460.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.400.000</t>
+          <t>Rp19.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.265.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.910.000</t>
+          <t>Rp4.080.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.289.000</t>
+          <t>Rp3.539.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.145.000</t>
+          <t>Rp1.895.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp22.050.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.008.000</t>
+          <t>Rp3.572.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp25.246.000</t>
+          <t>Rp28.141.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp9.125.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>96</v>
       </c>
       <c r="D50" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.741.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.310.000</t>
+          <t>Rp17.810.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp10.490.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.799.976</t>
+          <t>Rp5.199.974</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp5.560.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp13.850.000</t>
+          <t>Rp13.150.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.610.000</t>
+          <t>Rp7.770.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.799.971</t>
+          <t>Rp6.599.967</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.185.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp4.235.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp7.420.000</t>
+          <t>Rp6.580.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>51</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.042.000</t>
+          <t>Rp3.211.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp7.020.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-18.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.300.000</t>
+          <t>Rp15.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.158.000</t>
+          <t>Rp4.257.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.936.000</t>
+          <t>Rp2.112.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.490.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.130.000</t>
+          <t>Rp16.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp12.700.000</t>
+          <t>Rp13.000.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.838.000</t>
+          <t>Rp3.057.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp855.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.820.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.531.000</t>
+          <t>Rp1.690.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp934.000</t>
+          <t>Rp1.374.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.886.000</t>
+          <t>Rp3.284.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp2.110.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.752.000</t>
+          <t>Rp5.247.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.448.000</t>
+          <t>Rp13.226.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.196.000</t>
+          <t>Rp5.096.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp13.300.000</t>
+          <t>Rp13.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp41.715.000</t>
+          <t>Rp42.375.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp951.000</t>
+          <t>Rp1.097.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp62.200.000</t>
+          <t>Rp62.900.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp564.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp23.110.000</t>
+          <t>Rp23.260.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.495.000</t>
+          <t>Rp9.245.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.948.000</t>
+          <t>Rp4.324.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.200.000</t>
+          <t>Rp20.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.080.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.070.000</t>
+          <t>Rp5.790.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp22.500.000</t>
+          <t>Rp23.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.937.000</t>
+          <t>Rp1.043.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp288.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>96</v>
       </c>
       <c r="D50" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.741.000</t>
+          <t>Rp3.999.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.175.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.810.000</t>
+          <t>Rp17.310.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.490.000</t>
+          <t>Rp10.770.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.270.500</t>
+          <t>Rp1.501.500</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.560.000</t>
+          <t>Rp5.710.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.599.967</t>
+          <t>Rp6.999.965</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp4.655.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp3.620.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.235.000</t>
+          <t>Rp4.530.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.580.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp7.020.000</t>
+          <t>Rp6.840.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-18.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.780.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.800.000</t>
+          <t>Rp16.300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.257.000</t>
+          <t>Rp4.554.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.490.000</t>
+          <t>Rp3.715.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp5.140.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.560.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.401.000</t>
+          <t>Rp3.580.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.304.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp2.178.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp5.247.000</t>
+          <t>Rp5.297.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp435.000</t>
+          <t>Rp735.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp13.750.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.114.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp474.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.000.000</t>
+          <t>Rp20.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp5.751.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp23.050.000</t>
+          <t>Rp23.450.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
